--- a/胎壓檢測器資料庫_V10/PEUGEOT_Data.xlsx
+++ b/胎壓檢測器資料庫_V10/PEUGEOT_Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J717"/>
+  <dimension ref="A1:J744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29146,17 +29146,17 @@
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2018-01 ~ 至今</t>
         </is>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>1889, 2525</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>AAV, ABE, AED</t>
         </is>
       </c>
       <c r="G712" t="inlineStr"/>
@@ -29192,7 +29192,7 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>ABR</t>
+          <t>ABR, ACA</t>
         </is>
       </c>
       <c r="G713" t="inlineStr"/>
@@ -29218,17 +29218,17 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2018-01 ~ 至今</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>1889, 2525</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>AEC</t>
+          <t>AAT, ABB, AEC</t>
         </is>
       </c>
       <c r="G714" t="inlineStr"/>
@@ -29254,17 +29254,17 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2018-01 ~ 至今</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>1889, 2525</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>AEB</t>
+          <t>AAG, AAI, AEB</t>
         </is>
       </c>
       <c r="G715" t="inlineStr"/>
@@ -29285,22 +29285,22 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>75 kWh</t>
+          <t>1.5 BlueHdi 75</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>2024-01 ~ 至今</t>
+          <t>2018-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>AEE, AEM</t>
+          <t>AAS, ABL</t>
         </is>
       </c>
       <c r="G716" t="inlineStr"/>
@@ -29321,12 +29321,12 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>e-Rifter</t>
+          <t>1.6 HDi 100</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>2021-01 ~ 2024-01</t>
+          <t>2018-01 ~ 2024-01</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>AED, AHT</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="G717" t="inlineStr"/>
@@ -29344,6 +29344,994 @@
       <c r="I717" t="inlineStr"/>
       <c r="J717" t="inlineStr"/>
     </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Rifter</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>1.6 HDi 75</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>2018-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>ABD</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr"/>
+      <c r="J718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Rifter</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>75 kWh</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>AEE, AEM</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr"/>
+      <c r="J719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Rifter</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>e-Rifter</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>2021-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>AED, AHT</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
+      <c r="J720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Roadcamp R</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr"/>
+      <c r="J721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Roadcruiser</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="inlineStr"/>
+      <c r="J722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Roadstar</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
+      <c r="J723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>2.2 HDi</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>BBE, BBF</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr"/>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="inlineStr"/>
+      <c r="J725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Summit L Shine</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr"/>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="inlineStr"/>
+      <c r="J726" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Summit Plus</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr"/>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr"/>
+      <c r="J727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Summit Prime</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr"/>
+      <c r="I728" t="inlineStr"/>
+      <c r="J728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Summit Q Shine</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr"/>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr"/>
+      <c r="J729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Summit Shine</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr"/>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr"/>
+      <c r="J730" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>1.5 BlueHDi</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>2018-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>AZX, AZY</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr"/>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>2.0 BlueHDi</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>2018-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>BAD, BBX</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr"/>
+      <c r="H732" t="inlineStr"/>
+      <c r="I732" t="inlineStr"/>
+      <c r="J732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>2.2 Diesel 145</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>2025-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>BFB</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr"/>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="inlineStr"/>
+      <c r="J733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>2.2 Diesel 180</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>2025-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>BFA</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr"/>
+      <c r="H734" t="inlineStr"/>
+      <c r="I734" t="inlineStr"/>
+      <c r="J734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>BlueHDi 115</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>2016-01 ~ 2018-01</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>AXB</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr"/>
+      <c r="J735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>BlueHDi 150</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>2016-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>AWR, AXC</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="inlineStr"/>
+      <c r="J736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>BlueHDi 180</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>2016-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>AXD</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr"/>
+      <c r="J737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>BlueHDi 95</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>2016-01 ~ 2018-01</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>AWQ</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr"/>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr"/>
+      <c r="J738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>2020-01 ~ 2024-01</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="inlineStr"/>
+      <c r="J739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Traveller</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>electric Long Range</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>2024-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>BED</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="inlineStr"/>
+      <c r="J740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Trenta</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr"/>
+      <c r="J741" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Trenta R</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr"/>
+      <c r="J742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Vario</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>2.2 HDI</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>2022-01 ~ 至今</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>3003, 4136</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>ZZZ</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr"/>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr"/>
+      <c r="J743" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>PEUGEOT</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>iOn</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>2010-01 ~ 2020-01</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>AOG</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>10/2014 -</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>TG1C | S180052094Z (Ident: A2C3781940780 / 2910000063200), TG1D | 2910000063200 (Ident: A2C3781940780 / S180052094Z)</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>VDO</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
